--- a/data/Vege.xlsx
+++ b/data/Vege.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HP Files\PhD_UM\Research\Study2_GBTM\Calculation_Oct_Dec_25\14a.MULTINOMIAL MINI_FINAL\Forest plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382CC4DC-3D8E-44E7-B312-6B00E5A6379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{382CC4DC-3D8E-44E7-B312-6B00E5A6379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD272B9-CEAA-4558-AC63-D68355700023}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="2325" windowWidth="38640" windowHeight="21120" xr2:uid="{EA73BA3A-ABA0-43A0-904B-DB55A24A3F16}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,6 +38,78 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="25">
   <si>
+    <t>FIT</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>CI_Lower</t>
+  </si>
+  <si>
+    <t>CI_Upper</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>Labels</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>men</t>
+  </si>
+  <si>
+    <t>sex (men)</t>
+  </si>
+  <si>
+    <t>Habit, tr3</t>
+  </si>
+  <si>
+    <t>Habit Strength, tr3</t>
+  </si>
+  <si>
+    <t>Habit, tr4</t>
+  </si>
+  <si>
+    <t>Habit Strength, tr4</t>
+  </si>
+  <si>
+    <t>Habit, tr5</t>
+  </si>
+  <si>
+    <t>Habit Strength, tr5</t>
+  </si>
+  <si>
+    <t>Self-Efficacy, tr2</t>
+  </si>
+  <si>
+    <t>Self-Efficacy Expectations, tr2</t>
+  </si>
+  <si>
+    <t>Self-Efficacy, tr3</t>
+  </si>
+  <si>
+    <t>Self-Efficacy Expectations, tr3</t>
+  </si>
+  <si>
+    <t>Self-Efficacy, tr4</t>
+  </si>
+  <si>
+    <t>Self-Efficacy Expectations, tr4</t>
+  </si>
+  <si>
+    <t>Self-Efficacy, tr5</t>
+  </si>
+  <si>
+    <t>Self-Efficacy Expectations, tr5</t>
+  </si>
+  <si>
     <r>
       <t>.</t>
     </r>
@@ -51,78 +123,6 @@
       <t>c</t>
     </r>
   </si>
-  <si>
-    <t>FIT</t>
-  </si>
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>p_value</t>
-  </si>
-  <si>
-    <t>CI_Lower</t>
-  </si>
-  <si>
-    <t>CI_Upper</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>men</t>
-  </si>
-  <si>
-    <t>Habit, tr3</t>
-  </si>
-  <si>
-    <t>Habit, tr4</t>
-  </si>
-  <si>
-    <t>Habit, tr5</t>
-  </si>
-  <si>
-    <t>Self-Efficacy, tr2</t>
-  </si>
-  <si>
-    <t>Self-Efficacy, tr3</t>
-  </si>
-  <si>
-    <t>Self-Efficacy, tr4</t>
-  </si>
-  <si>
-    <t>Self-Efficacy, tr5</t>
-  </si>
-  <si>
-    <t>Labels</t>
-  </si>
-  <si>
-    <t>sex (men)</t>
-  </si>
-  <si>
-    <t>Habit Strenght, tr3</t>
-  </si>
-  <si>
-    <t>Habit Strenght, tr4</t>
-  </si>
-  <si>
-    <t>Habit Strenght, tr5</t>
-  </si>
-  <si>
-    <t>Self-Efficacy Expectations, tr2</t>
-  </si>
-  <si>
-    <t>Self-Efficacy Expectations, tr3</t>
-  </si>
-  <si>
-    <t>Self-Efficacy Expectations, tr4</t>
-  </si>
-  <si>
-    <t>Self-Efficacy Expectations, tr5</t>
-  </si>
 </sst>
 </file>
 
@@ -131,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,38 +672,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8633AFC9-366B-4C92-8B0C-5B3AA80F5F61}">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="20.53125" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18.3984375" customWidth="1"/>
-    <col min="7" max="7" width="14.3984375" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="15.4">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2">
         <v>2</v>
       </c>
@@ -726,7 +726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="30">
       <c r="A3">
         <v>2</v>
       </c>
@@ -746,15 +746,15 @@
         <v>0.13051427498783558</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30.75">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5">
         <v>1.6698889842848099</v>
@@ -769,15 +769,15 @@
         <v>1.2873637784687988E-2</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30.75">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5">
         <v>2.0789382132262046</v>
@@ -792,15 +792,15 @@
         <v>3.1349646082779164E-3</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30.75">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" s="5">
         <v>2.1508076992252256</v>
@@ -815,15 +815,15 @@
         <v>6.4454179941236269E-4</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="60">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" s="5">
         <v>0.83604218293931842</v>
@@ -838,15 +838,15 @@
         <v>0.74927913842160676</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45">
       <c r="A8">
         <v>2</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" s="13">
         <v>4.2548583416816879</v>
@@ -861,15 +861,15 @@
         <v>2.2621028015128587E-4</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C9" s="13">
         <v>8.7698138719251642</v>
@@ -884,15 +884,15 @@
         <v>5.7754257164620855E-8</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60">
       <c r="A10">
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5">
         <v>13.740899330634802</v>
@@ -907,10 +907,10 @@
         <v>3.3603787908340521E-9</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
       <c r="A11">
         <v>3</v>
       </c>
@@ -933,7 +933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="30">
       <c r="A12">
         <v>3</v>
       </c>
@@ -953,15 +953,15 @@
         <v>0.24230255677095336</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30.75">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5">
         <v>1.8320576895186755</v>
@@ -976,15 +976,15 @@
         <v>3.28964307646087E-2</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30.75">
       <c r="A14">
         <v>3</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5">
         <v>2.2382667764203932</v>
@@ -999,15 +999,15 @@
         <v>1.5749205663420689E-2</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30.75">
       <c r="A15">
         <v>3</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" s="5">
         <v>2.710870016279201</v>
@@ -1022,15 +1022,15 @@
         <v>8.6143491154603788E-4</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="60">
       <c r="A16">
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5">
         <v>0.71900786597958055</v>
@@ -1045,15 +1045,15 @@
         <v>0.5604921935097853</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="45">
       <c r="A17">
         <v>3</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C17" s="13">
         <v>1.6350024620338497</v>
@@ -1068,15 +1068,15 @@
         <v>0.24181636420730968</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45">
       <c r="A18">
         <v>3</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C18" s="13">
         <v>3.9099094190399812</v>
@@ -1091,15 +1091,15 @@
         <v>1.4145234371468582E-3</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="60">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19" s="5">
         <v>7.8011871609396817</v>
@@ -1114,10 +1114,10 @@
         <v>1.7475063984980723E-5</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
       <c r="A20">
         <v>4</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" ht="30">
       <c r="A21">
         <v>4</v>
       </c>
@@ -1160,15 +1160,15 @@
         <v>0.56749827132866293</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30.75">
       <c r="A22">
         <v>4</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="5">
         <v>1.4836881246497033</v>
@@ -1183,15 +1183,15 @@
         <v>3.0748153617780528E-2</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30.75">
       <c r="A23">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C23" s="5">
         <v>1.8357761304158944</v>
@@ -1206,15 +1206,15 @@
         <v>5.6938275613456317E-3</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30.75">
       <c r="A24">
         <v>4</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" s="5">
         <v>2.3861226962646014</v>
@@ -1229,15 +1229,15 @@
         <v>1.0310228313052176E-5</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60">
       <c r="A25">
         <v>4</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C25" s="5">
         <v>1.5242284559605661</v>
@@ -1252,15 +1252,15 @@
         <v>0.24890725233511868</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="45">
       <c r="A26">
         <v>4</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C26" s="13">
         <v>3.6394838425631932</v>
@@ -1275,15 +1275,15 @@
         <v>1.5577044807169524E-5</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="45">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C27" s="13">
         <v>4.9229552983851654</v>
@@ -1298,15 +1298,15 @@
         <v>4.0092668441705808E-7</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="60">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C28" s="5">
         <v>7.3871267882755678</v>
@@ -1321,10 +1321,10 @@
         <v>3.132435980467921E-8</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15">
       <c r="A29">
         <v>5</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" ht="30">
       <c r="A30">
         <v>5</v>
       </c>
@@ -1367,15 +1367,15 @@
         <v>2.206267266652974E-2</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30.75">
       <c r="A31">
         <v>5</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="5">
         <v>3.0810243666506167</v>
@@ -1390,15 +1390,15 @@
         <v>4.853087740617499E-2</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30.75">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C32" s="5">
         <v>4.6079970451053649</v>
@@ -1413,15 +1413,15 @@
         <v>9.7575608948158778E-3</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30.75">
       <c r="A33">
         <v>5</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C33" s="5">
         <v>7.6482438380199218</v>
@@ -1436,15 +1436,15 @@
         <v>1.3524395514746097E-4</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="60">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C34" s="5">
         <v>1.0109228567122992</v>
@@ -1453,21 +1453,21 @@
         <v>0</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F34" s="5">
         <v>0.99999562192724711</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="45">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C35" s="13">
         <v>11488569.365267461</v>
@@ -1482,15 +1482,15 @@
         <v>2.3105657643861725E-278</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="45" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="45">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C36" s="13">
         <v>44336249.286410771</v>
@@ -1505,15 +1505,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="60">
       <c r="A37">
         <v>5</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C37" s="5">
         <v>114993456.88080512</v>
@@ -1526,10 +1526,10 @@
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15">
       <c r="B38" s="10"/>
       <c r="C38" s="1"/>
       <c r="D38" s="10"/>
@@ -1537,7 +1537,7 @@
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
     </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" ht="15">
       <c r="B39" s="10"/>
       <c r="C39" s="1"/>
       <c r="D39" s="10"/>
@@ -1545,7 +1545,7 @@
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" ht="15">
       <c r="B40" s="10"/>
       <c r="C40" s="1"/>
       <c r="D40" s="10"/>

--- a/data/Vege.xlsx
+++ b/data/Vege.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HP Files\PhD_UM\Research\Study2_GBTM\Calculation_Oct_Dec_25\14a.MULTINOMIAL MINI_FINAL\Forest plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{382CC4DC-3D8E-44E7-B312-6B00E5A6379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD272B9-CEAA-4558-AC63-D68355700023}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDB9850-E650-4526-9FBC-359254E093D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2325" windowWidth="38640" windowHeight="21120" xr2:uid="{EA73BA3A-ABA0-43A0-904B-DB55A24A3F16}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA73BA3A-ABA0-43A0-904B-DB55A24A3F16}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -116,9 +116,10 @@
     <r>
       <rPr>
         <vertAlign val="superscript"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color indexed="60"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>c</t>
     </r>
@@ -131,7 +132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0.000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,14 +155,26 @@
       <name val="Arial"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
       <sz val="12"/>
+      <color indexed="62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color indexed="60"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="62"/>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color indexed="60"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -288,12 +301,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -311,19 +325,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -335,11 +343,24 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{865BDE1A-3A69-4143-9900-224C64AB13E9}"/>
     <cellStyle name="Normal_Sheet2" xfId="2" xr:uid="{5A22568A-CE35-42C6-B7B5-08B401C960F5}"/>
+    <cellStyle name="Normal_Sheet3" xfId="3" xr:uid="{B9C483DD-D674-43F7-9A86-C4C74F188B87}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -672,19 +693,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8633AFC9-366B-4C92-8B0C-5B3AA80F5F61}">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.3984375" customWidth="1"/>
+    <col min="7" max="7" width="14.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.4">
+    <row r="1" spans="1:7" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -699,11 +720,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2</v>
       </c>
@@ -726,7 +747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -749,11 +770,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30.75">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="5">
@@ -768,22 +789,22 @@
       <c r="F4" s="5">
         <v>1.2873637784687988E-2</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30.75">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="5">
         <v>2.0789382132262046</v>
       </c>
       <c r="D5" s="5">
-        <v>1.2792884617172144</v>
+        <v>1.27928846171721</v>
       </c>
       <c r="E5" s="6">
         <v>3.3784281057383088</v>
@@ -791,15 +812,15 @@
       <c r="F5" s="5">
         <v>3.1349646082779164E-3</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30.75">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="5">
@@ -814,11 +835,11 @@
       <c r="F6" s="5">
         <v>6.4454179941236269E-4</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2</v>
       </c>
@@ -841,53 +862,53 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>4.2548583416816879</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>1.9708297292679735</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>9.1858871615979503</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <v>2.2621028015128587E-4</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>8.7698138719251642</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>4.0025997580751653</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>19.214920300998717</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="11">
         <v>5.7754257164620855E-8</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="60">
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2</v>
       </c>
@@ -910,650 +931,651 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5">
-        <v>0.95965254979702563</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.93339263937288075</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.98665125209331073</v>
-      </c>
-      <c r="F11" s="5">
-        <v>3.6225567186944593E-3</v>
+      <c r="C11" s="13">
+        <v>0.96736090221368398</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.94931103028910335</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0.98575396816645844</v>
+      </c>
+      <c r="F11" s="13">
+        <v>5.5428621792408619E-4</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>0.79341551975649149</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.53831701891360639</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.169400492410388</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0.24230255677095336</v>
+      <c r="C12" s="13">
+        <v>0.92575354416282052</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0.71062292695016038</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1.2060117849112548</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0.56749827132866448</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>3</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="5">
-        <v>1.8320576895186755</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.0504359386017685</v>
-      </c>
-      <c r="E13" s="6">
-        <v>3.1952785071236671</v>
-      </c>
-      <c r="F13" s="5">
-        <v>3.28964307646087E-2</v>
-      </c>
-      <c r="G13" s="11" t="s">
+      <c r="C13" s="13">
+        <v>1.4836881246497025</v>
+      </c>
+      <c r="D13" s="13">
+        <v>1.0372673640048664</v>
+      </c>
+      <c r="E13" s="14">
+        <v>2.1222401548692935</v>
+      </c>
+      <c r="F13" s="13">
+        <v>3.0748153617780719E-2</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30.75">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5">
-        <v>2.2382667764203932</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1.1638380510952679</v>
-      </c>
-      <c r="E14" s="6">
-        <v>4.3045835781985868</v>
-      </c>
-      <c r="F14" s="5">
-        <v>1.5749205663420689E-2</v>
-      </c>
-      <c r="G14" s="11" t="s">
+      <c r="C14" s="13">
+        <v>1.8357761304158937</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1.1934540696346247</v>
+      </c>
+      <c r="E14" s="14">
+        <v>2.8237986586584758</v>
+      </c>
+      <c r="F14" s="13">
+        <v>5.6938275613456673E-3</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30.75">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>3</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.710870016279201</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1.5078685874063726</v>
-      </c>
-      <c r="E15" s="6">
-        <v>4.8736450288430078</v>
-      </c>
-      <c r="F15" s="5">
-        <v>8.6143491154603788E-4</v>
-      </c>
-      <c r="G15" s="11" t="s">
+      <c r="C15" s="13">
+        <v>2.3861226962646009</v>
+      </c>
+      <c r="D15" s="13">
+        <v>1.6212643115475063</v>
+      </c>
+      <c r="E15" s="14">
+        <v>3.5118157360748246</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1.0310228313051205E-5</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="60">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.71900786597958055</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.23678620405429035</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2.1832872966787331</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0.5604921935097853</v>
+      <c r="C16" s="13">
+        <v>1.5242284559605659</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0.74454098159273407</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3.1204090082320901</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0.24890725233512667</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="45">
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="13">
-        <v>1.6350024620338497</v>
+        <v>3.6394838425631932</v>
       </c>
       <c r="D17" s="13">
-        <v>0.71775502674488167</v>
+        <v>2.0254438962569137</v>
       </c>
       <c r="E17" s="14">
-        <v>3.7244365434544311</v>
+        <v>6.5397232995479637</v>
       </c>
       <c r="F17" s="13">
-        <v>0.24181636420730968</v>
-      </c>
-      <c r="G17" s="12" t="s">
+        <v>1.5577044807173783E-5</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="45">
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>3</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="13">
-        <v>3.9099094190399812</v>
+        <v>4.9229552983851672</v>
       </c>
       <c r="D18" s="13">
-        <v>1.6924847721658989</v>
+        <v>2.6579478741612514</v>
       </c>
       <c r="E18" s="14">
-        <v>9.0325135661540124</v>
+        <v>9.1181204513073446</v>
       </c>
       <c r="F18" s="13">
-        <v>1.4145234371468582E-3</v>
-      </c>
-      <c r="G18" s="12" t="s">
+        <v>4.0092668441712785E-7</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60">
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>3</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="5">
-        <v>7.8011871609396817</v>
-      </c>
-      <c r="D19" s="5">
-        <v>3.0551221345747495</v>
-      </c>
-      <c r="E19" s="6">
-        <v>19.920159796976883</v>
-      </c>
-      <c r="F19" s="5">
-        <v>1.7475063984980723E-5</v>
+      <c r="C19" s="13">
+        <v>7.3871267882755713</v>
+      </c>
+      <c r="D19" s="13">
+        <v>3.6381640108716331</v>
+      </c>
+      <c r="E19" s="14">
+        <v>14.999225439807685</v>
+      </c>
+      <c r="F19" s="13">
+        <v>3.1324359804682215E-8</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15">
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="5">
-        <v>0.96736090221368409</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.94931103028910713</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.98575396816645466</v>
-      </c>
-      <c r="F20" s="5">
-        <v>5.5428621792261374E-4</v>
+      <c r="C20" s="13">
+        <v>0.95965254979702541</v>
+      </c>
+      <c r="D20" s="13">
+        <v>0.9333926393728722</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0.98665125209331939</v>
+      </c>
+      <c r="F20" s="13">
+        <v>3.6225567187051864E-3</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>4</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5">
-        <v>0.92575354416282085</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.71062292695016238</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.2060117849112524</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.56749827132866293</v>
+      <c r="C21" s="13">
+        <v>0.79341551975649127</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0.53831701891360484</v>
+      </c>
+      <c r="E21" s="14">
+        <v>1.1694004924103909</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0.24230255677095613</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30.75">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>4</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>1.4836881246497033</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1.0372673640048671</v>
-      </c>
-      <c r="E22" s="6">
-        <v>2.1222401548692944</v>
-      </c>
-      <c r="F22" s="5">
-        <v>3.0748153617780528E-2</v>
-      </c>
-      <c r="G22" s="11" t="s">
+      <c r="C22" s="13">
+        <v>1.8320576895186749</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1.0504359386017685</v>
+      </c>
+      <c r="E22" s="14">
+        <v>3.1952785071236649</v>
+      </c>
+      <c r="F22" s="13">
+        <v>3.2896430764608582E-2</v>
+      </c>
+      <c r="G22" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30.75">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>4</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="5">
-        <v>1.8357761304158944</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1.1934540696346252</v>
-      </c>
-      <c r="E23" s="6">
-        <v>2.8237986586584771</v>
-      </c>
-      <c r="F23" s="5">
-        <v>5.6938275613456317E-3</v>
-      </c>
-      <c r="G23" s="11" t="s">
+      <c r="C23" s="13">
+        <v>2.2382667764203945</v>
+      </c>
+      <c r="D23" s="13">
+        <v>1.1638380510952686</v>
+      </c>
+      <c r="E23" s="14">
+        <v>4.3045835781985886</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1.5749205663420661E-2</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30.75">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>4</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="5">
-        <v>2.3861226962646014</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1.6212643115475036</v>
-      </c>
-      <c r="E24" s="6">
-        <v>3.5118157360748317</v>
-      </c>
-      <c r="F24" s="5">
-        <v>1.0310228313052176E-5</v>
-      </c>
-      <c r="G24" s="11" t="s">
+      <c r="C24" s="13">
+        <v>2.7108700162792041</v>
+      </c>
+      <c r="D24" s="13">
+        <v>1.5078685874063757</v>
+      </c>
+      <c r="E24" s="14">
+        <v>4.8736450288430078</v>
+      </c>
+      <c r="F24" s="13">
+        <v>8.6143491154600882E-4</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="60">
+    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>4</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="5">
-        <v>1.5242284559605661</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0.74454098159274273</v>
-      </c>
-      <c r="E25" s="6">
-        <v>3.1204090082320555</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0.24890725233511868</v>
+      <c r="C25" s="13">
+        <v>0.71900786597957889</v>
+      </c>
+      <c r="D25" s="13">
+        <v>0.23678620405428863</v>
+      </c>
+      <c r="E25" s="14">
+        <v>2.1832872966787393</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.56049219350978419</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="45">
+    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>4</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="13">
-        <v>3.6394838425631932</v>
+        <v>1.6350024620338459</v>
       </c>
       <c r="D26" s="13">
-        <v>2.0254438962569306</v>
+        <v>0.71775502674487712</v>
       </c>
       <c r="E26" s="14">
-        <v>6.5397232995479104</v>
+        <v>3.7244365434544382</v>
       </c>
       <c r="F26" s="13">
-        <v>1.5577044807169524E-5</v>
-      </c>
-      <c r="G26" s="12" t="s">
+        <v>0.24181636420731412</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="45">
+    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>4</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="13">
-        <v>4.9229552983851654</v>
+        <v>3.909909419039975</v>
       </c>
       <c r="D27" s="13">
-        <v>2.6579478741612617</v>
+        <v>1.692484772165894</v>
       </c>
       <c r="E27" s="14">
-        <v>9.1181204513073038</v>
+        <v>9.032513566154007</v>
       </c>
       <c r="F27" s="13">
-        <v>4.0092668441705808E-7</v>
-      </c>
-      <c r="G27" s="12" t="s">
+        <v>1.4145234371469035E-3</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="60">
+    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="5">
-        <v>7.3871267882755678</v>
-      </c>
-      <c r="D28" s="5">
-        <v>3.6381640108716402</v>
-      </c>
-      <c r="E28" s="6">
-        <v>14.999225439807637</v>
-      </c>
-      <c r="F28" s="5">
-        <v>3.132435980467921E-8</v>
+      <c r="C28" s="13">
+        <v>7.8011871609396684</v>
+      </c>
+      <c r="D28" s="13">
+        <v>3.0551221345747419</v>
+      </c>
+      <c r="E28" s="14">
+        <v>19.920159796976865</v>
+      </c>
+      <c r="F28" s="13">
+        <v>1.7475063984981187E-5</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15">
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>5</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="5">
-        <v>0.92198585441599668</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0.88658929489279181</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.95879560089430815</v>
-      </c>
-      <c r="F29" s="5">
-        <v>4.7706830421431327E-5</v>
+      <c r="C29" s="13">
+        <v>0.92198585441599701</v>
+      </c>
+      <c r="D29" s="13">
+        <v>0.88658929489278893</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0.95879560089431215</v>
+      </c>
+      <c r="F29" s="13">
+        <v>4.7706830421515393E-5</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30">
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>5</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="5">
-        <v>0.52535062443472091</v>
-      </c>
-      <c r="D30" s="5">
-        <v>0.30277011597129166</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.91156050097137253</v>
-      </c>
-      <c r="F30" s="5">
-        <v>2.206267266652974E-2</v>
+      <c r="C30" s="13">
+        <v>0.52535062443472003</v>
+      </c>
+      <c r="D30" s="13">
+        <v>0.30277011597129111</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0.91156050097137098</v>
+      </c>
+      <c r="F30" s="13">
+        <v>2.2062672666529486E-2</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30.75">
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>5</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="5">
-        <v>3.0810243666506167</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1.0072856603172808</v>
-      </c>
-      <c r="E31" s="6">
-        <v>9.4240507155683773</v>
-      </c>
-      <c r="F31" s="5">
-        <v>4.853087740617499E-2</v>
-      </c>
-      <c r="G31" s="11" t="s">
+      <c r="C31" s="13">
+        <v>3.0810243666505626</v>
+      </c>
+      <c r="D31" s="13">
+        <v>1.0072856603172733</v>
+      </c>
+      <c r="E31" s="14">
+        <v>9.4240507155681179</v>
+      </c>
+      <c r="F31" s="13">
+        <v>4.8530877406176412E-2</v>
+      </c>
+      <c r="G31" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30.75">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>5</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="5">
-        <v>4.6079970451053649</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1.4464302467508729</v>
-      </c>
-      <c r="E32" s="6">
-        <v>14.68002816962453</v>
-      </c>
-      <c r="F32" s="5">
-        <v>9.7575608948158778E-3</v>
-      </c>
-      <c r="G32" s="11" t="s">
+      <c r="C32" s="13">
+        <v>4.6079970451052858</v>
+      </c>
+      <c r="D32" s="13">
+        <v>1.4464302467508614</v>
+      </c>
+      <c r="E32" s="14">
+        <v>14.680028169624144</v>
+      </c>
+      <c r="F32" s="13">
+        <v>9.7575608948161207E-3</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30.75">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>5</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="5">
-        <v>7.6482438380199218</v>
-      </c>
-      <c r="D33" s="5">
-        <v>2.6905016279463965</v>
-      </c>
-      <c r="E33" s="6">
-        <v>21.741534440348282</v>
-      </c>
-      <c r="F33" s="5">
-        <v>1.3524395514746097E-4</v>
-      </c>
-      <c r="G33" s="11" t="s">
+      <c r="C33" s="13">
+        <v>7.6482438380197957</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2.6905016279463845</v>
+      </c>
+      <c r="E33" s="14">
+        <v>21.741534440347664</v>
+      </c>
+      <c r="F33" s="13">
+        <v>1.3524395514745376E-4</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="60">
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="5">
-        <v>1.0109228567122992</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" s="13">
+        <v>1.0109227542118022</v>
+      </c>
+      <c r="D34" s="13">
         <v>0</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="5">
-        <v>0.99999562192724711</v>
+      <c r="F34" s="13">
+        <v>0.99999562196810876</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="45">
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="13">
-        <v>11488569.365267461</v>
+        <v>11488568.200406734</v>
       </c>
       <c r="D35" s="13">
-        <v>4700163.5108748088</v>
+        <v>4700163.0343110254</v>
       </c>
       <c r="E35" s="14">
-        <v>28081411.583912402</v>
+        <v>28081408.736653414</v>
       </c>
       <c r="F35" s="13">
-        <v>2.3105657643861725E-278</v>
-      </c>
-      <c r="G35" s="12" t="s">
+        <v>2.3105840944994127E-278</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="45">
+    <row r="36" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="13">
-        <v>44336249.286410771</v>
+        <v>44336244.791024782</v>
       </c>
       <c r="D36" s="13">
-        <v>21901373.4382402</v>
+        <v>21901371.217593916</v>
       </c>
       <c r="E36" s="14">
-        <v>89752499.144852981</v>
+        <v>89752490.044576481</v>
       </c>
       <c r="F36" s="13">
         <v>0</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="60">
+    <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>5</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="5">
-        <v>114993456.88080512</v>
-      </c>
-      <c r="D37" s="5">
-        <v>114993456.88080512</v>
-      </c>
-      <c r="E37" s="6">
-        <v>114993456.88080512</v>
-      </c>
-      <c r="F37" s="7"/>
+      <c r="C37" s="13">
+        <v>114993445.22127181</v>
+      </c>
+      <c r="D37" s="13">
+        <v>114993445.22127181</v>
+      </c>
+      <c r="E37" s="14">
+        <v>114993445.22127181</v>
+      </c>
+      <c r="F37" s="15"/>
       <c r="G37" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15">
-      <c r="B38" s="10"/>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+      <c r="B38" s="8"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-    </row>
-    <row r="39" spans="1:7" ht="15">
-      <c r="B39" s="10"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+      <c r="B39" s="8"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-    </row>
-    <row r="40" spans="1:7" ht="15">
-      <c r="B40" s="10"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.45">
+      <c r="B40" s="8"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>